--- a/data/usa/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/usa/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD26"/>
+  <dimension ref="A1:CD27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,102 +590,102 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>total_passes_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>total_passes_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_away</t>
-        </is>
-      </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
           <t>red_cards_home</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>red_cards_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_home</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_away</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
@@ -842,286 +842,296 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR2B69AM</t>
+          <t>AwME1KOf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45557.80208333334</v>
+        <v>45563.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">chapman a 
+  usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18500</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>72000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30015</v>
+      </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="n">
         <v>11</v>
       </c>
-      <c r="P2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>28</v>
-      </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>432</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>349</v>
+        <v>394</v>
       </c>
       <c r="AJ2" t="n">
-        <v>369</v>
+        <v>689</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>342</v>
       </c>
       <c r="AL2" t="n">
-        <v>7</v>
+        <v>616</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>nJ01AhXP</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="AS2" t="n">
         <v>167</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
         <v>1671</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AU2" t="n">
         <v>0</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AV2" t="n">
         <v>2024</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
       <c r="BC2" t="n">
-        <v>25.4</v>
+        <v>26.77777777777778</v>
       </c>
       <c r="BD2" t="n">
-        <v>184.4</v>
+        <v>179.5555555555555</v>
       </c>
       <c r="BE2" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5900</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
-        <v>26.9</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="BH2" t="n">
-        <v>183.8</v>
+        <v>179.9090909090909</v>
       </c>
       <c r="BI2" t="n">
-        <v>67</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
+        <v>67.90909090909091</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>3636.363636363636</v>
+      </c>
       <c r="BK2" t="n">
-        <v>25.9</v>
+        <v>21.14285714285714</v>
       </c>
       <c r="BL2" t="n">
-        <v>182.85</v>
+        <v>180.7142857142857</v>
       </c>
       <c r="BM2" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4600</v>
-      </c>
+        <v>62.35714285714285</v>
+      </c>
+      <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="n">
-        <v>24.94736842105263</v>
+        <v>24.90476190476191</v>
       </c>
       <c r="BP2" t="n">
-        <v>180.2631578947368</v>
+        <v>180.8571428571429</v>
       </c>
       <c r="BQ2" t="n">
-        <v>62.31578947368421</v>
+        <v>61.61904761904762</v>
       </c>
       <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>26.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BU2" t="n">
-        <v>56</v>
+        <v>68.75</v>
       </c>
       <c r="BV2" t="inlineStr"/>
       <c r="BW2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BX2" t="n">
-        <v>56</v>
+        <v>275</v>
       </c>
       <c r="BY2" t="n">
-        <v>17.5</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="BZ2" t="n">
-        <v>189</v>
+        <v>176.6666666666667</v>
       </c>
       <c r="CA2" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="CB2" t="inlineStr"/>
+        <v>69.33333333333333</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>5333.333333333333</v>
+      </c>
       <c r="CC2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CD2" t="n">
-        <v>109</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>E99Th5bD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45563.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">dickerson j 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27000</v>
+        <v>54405</v>
       </c>
       <c r="F3" t="n">
-        <v>25387</v>
+        <v>25902</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -1131,332 +1141,314 @@
         <v>43</v>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" t="n">
         <v>13</v>
       </c>
-      <c r="O3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>10</v>
-      </c>
-      <c r="V3" t="n">
-        <v>5</v>
-      </c>
       <c r="W3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG3" t="n">
-        <v>768</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>451</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>675</v>
+        <v>580</v>
       </c>
       <c r="AJ3" t="n">
-        <v>370</v>
+        <v>482</v>
       </c>
       <c r="AK3" t="n">
-        <v>11</v>
+        <v>493</v>
       </c>
       <c r="AL3" t="n">
-        <v>10</v>
+        <v>389</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>Sd7snoa0</t>
         </is>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="AS3" t="n">
         <v>167</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AT3" t="n">
         <v>1671</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2024</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>2024</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
       <c r="BB3" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>26.09090909090909</v>
+        <v>26.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>178.8181818181818</v>
+        <v>178.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>71.90909090909091</v>
+        <v>67.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>10181.81818181818</v>
+        <v>3600</v>
       </c>
       <c r="BG3" t="n">
-        <v>24.22222222222222</v>
+        <v>26.9</v>
       </c>
       <c r="BH3" t="n">
-        <v>181.3333333333333</v>
+        <v>179</v>
       </c>
       <c r="BI3" t="n">
-        <v>66.11111111111111</v>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
+        <v>69.2</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>3900</v>
+      </c>
       <c r="BK3" t="n">
-        <v>25.09523809523809</v>
+        <v>26.05555555555556</v>
       </c>
       <c r="BL3" t="n">
-        <v>178.3809523809524</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="BM3" t="n">
-        <v>66.9047619047619</v>
+        <v>67.22222222222223</v>
       </c>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="n">
-        <v>26.81818181818182</v>
+        <v>25.05555555555556</v>
       </c>
       <c r="BP3" t="n">
-        <v>176.4090909090909</v>
+        <v>180.1666666666667</v>
       </c>
       <c r="BQ3" t="n">
-        <v>68.81818181818181</v>
+        <v>65.38888888888889</v>
       </c>
       <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>180</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>70</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>174.5</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>68</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>4500</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>136</v>
-      </c>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>ph6YLlA9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45563.89583333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">montero r 
-  cos </t>
+          <t xml:space="preserve">szpala l 
+  usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18000</v>
+        <v>20738</v>
       </c>
       <c r="F4" t="n">
-        <v>15112</v>
+        <v>20738</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>15</v>
+      </c>
+      <c r="W4" t="n">
+        <v>7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>16</v>
       </c>
-      <c r="N4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="AB4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC4" t="n">
         <v>6</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="AD4" t="n">
         <v>6</v>
       </c>
-      <c r="T4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>15</v>
-      </c>
-      <c r="V4" t="n">
-        <v>11</v>
-      </c>
-      <c r="W4" t="n">
-        <v>4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>572</v>
-      </c>
       <c r="AH4" t="n">
-        <v>429</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="AJ4" t="n">
-        <v>359</v>
+        <v>491</v>
       </c>
       <c r="AK4" t="n">
-        <v>6</v>
+        <v>384</v>
       </c>
       <c r="AL4" t="n">
-        <v>13</v>
+        <v>380</v>
       </c>
       <c r="AM4" t="n">
         <v>6</v>
@@ -1464,159 +1456,167 @@
       <c r="AN4" t="n">
         <v>1</v>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>bFuhdIb3</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>WSL0wFD4</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="AO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="AS4" t="n">
         <v>167</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
         <v>1671</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2024</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>2024</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>26.8</v>
+        <v>28.22222222222222</v>
       </c>
       <c r="BD4" t="n">
-        <v>179.9</v>
+        <v>180.8888888888889</v>
       </c>
       <c r="BE4" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="BF4" t="inlineStr"/>
+        <v>67.66666666666667</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5444.444444444444</v>
+      </c>
       <c r="BG4" t="n">
-        <v>26.18181818181818</v>
+        <v>25.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>182.7272727272727</v>
+        <v>181.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>68.72727272727273</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="BJ4" t="n">
-        <v>6727.272727272727</v>
+        <v>4800</v>
       </c>
       <c r="BK4" t="n">
-        <v>27.23809523809524</v>
+        <v>28.31578947368421</v>
       </c>
       <c r="BL4" t="n">
-        <v>177.8571428571429</v>
+        <v>178.3684210526316</v>
       </c>
       <c r="BM4" t="n">
-        <v>67.9047619047619</v>
-      </c>
-      <c r="BN4" t="inlineStr"/>
+        <v>67.31578947368421</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4052.631578947368</v>
+      </c>
       <c r="BO4" t="n">
-        <v>23.31578947368421</v>
+        <v>25.35294117647059</v>
       </c>
       <c r="BP4" t="n">
-        <v>180.8421052631579</v>
+        <v>178.7058823529412</v>
       </c>
       <c r="BQ4" t="n">
-        <v>63.1578947368421</v>
+        <v>65.88235294117646</v>
       </c>
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="n">
-        <v>24.16666666666667</v>
+        <v>31.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>183.8333333333333</v>
+        <v>189</v>
       </c>
       <c r="BU4" t="n">
-        <v>65.16666666666667</v>
+        <v>63</v>
       </c>
       <c r="BV4" t="n">
-        <v>2666.666666666667</v>
+        <v>2500</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BX4" t="n">
-        <v>391</v>
+        <v>126</v>
       </c>
       <c r="BY4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BZ4" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="CA4" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="CB4" t="n">
-        <v>3750</v>
+        <v>2000</v>
       </c>
       <c r="CC4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD4" t="n">
-        <v>272</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>UHiGG8jK</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45563.89583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t xml:space="preserve">montero r 
+  cos </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18061</v>
+        <v>61500</v>
       </c>
       <c r="F5" t="n">
-        <v>15896</v>
+        <v>16097</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1625,122 +1625,122 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>15</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>482</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>381</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>414</v>
+        <v>582</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300</v>
+        <v>361</v>
       </c>
       <c r="AK5" t="n">
-        <v>9</v>
+        <v>491</v>
       </c>
       <c r="AL5" t="n">
+        <v>284</v>
+      </c>
+      <c r="AM5" t="n">
         <v>7</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="AS5" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AU5" t="n">
         <v>0</v>
       </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>lAVQ9RGh</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AV5" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1757,418 +1757,420 @@
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>23.4</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="BD5" t="n">
-        <v>180.5</v>
+        <v>183.0909090909091</v>
       </c>
       <c r="BE5" t="n">
-        <v>64.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>25.4</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="BH5" t="n">
-        <v>184.6</v>
+        <v>181.1818181818182</v>
       </c>
       <c r="BI5" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
+        <v>67.45454545454545</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>4363.636363636364</v>
+      </c>
       <c r="BK5" t="n">
-        <v>23.38095238095238</v>
+        <v>25</v>
       </c>
       <c r="BL5" t="n">
-        <v>178.2857142857143</v>
+        <v>180.1666666666667</v>
       </c>
       <c r="BM5" t="n">
-        <v>62.61904761904762</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="n">
-        <v>24.68181818181818</v>
+        <v>24.26086956521739</v>
       </c>
       <c r="BP5" t="n">
-        <v>180.1818181818182</v>
+        <v>180.2608695652174</v>
       </c>
       <c r="BQ5" t="n">
-        <v>64.90909090909091</v>
+        <v>63.21739130434783</v>
       </c>
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="BT5" t="n">
-        <v>181.5</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="BU5" t="n">
-        <v>65.5</v>
+        <v>65</v>
       </c>
       <c r="BV5" t="n">
-        <v>2500</v>
+        <v>2333.333333333333</v>
       </c>
       <c r="BW5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BX5" t="n">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="BY5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BZ5" t="n">
-        <v>174.3333333333333</v>
+        <v>183.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="CB5" t="inlineStr"/>
       <c r="CC5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CD5" t="n">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>Or5xL8PF</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45563.89583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso t 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20213</v>
+        <v>20500</v>
       </c>
       <c r="F6" t="n">
-        <v>20778</v>
+        <v>19096</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V6" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
         <v>6</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z6" t="n">
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>451</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="AJ6" t="n">
-        <v>347</v>
+        <v>542</v>
       </c>
       <c r="AK6" t="n">
-        <v>5</v>
+        <v>385</v>
       </c>
       <c r="AL6" t="n">
-        <v>8</v>
+        <v>479</v>
       </c>
       <c r="AM6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>EqKWmJfM</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="AS6" t="n">
         <v>167</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AT6" t="n">
         <v>1671</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AU6" t="n">
         <v>0</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AV6" t="n">
         <v>2024</v>
       </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>nezMCpx2</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>23.6</v>
+        <v>26</v>
       </c>
       <c r="BD6" t="n">
-        <v>182.3</v>
+        <v>179.6363636363636</v>
       </c>
       <c r="BE6" t="n">
-        <v>62.8</v>
+        <v>68.90909090909091</v>
       </c>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
-        <v>24.81818181818182</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="BH6" t="n">
-        <v>176.6363636363636</v>
+        <v>179.7272727272727</v>
       </c>
       <c r="BI6" t="n">
-        <v>69.72727272727273</v>
+        <v>69.27272727272727</v>
       </c>
       <c r="BJ6" t="n">
-        <v>4454.545454545455</v>
+        <v>4363.636363636364</v>
       </c>
       <c r="BK6" t="n">
-        <v>26.21052631578947</v>
+        <v>24.58823529411765</v>
       </c>
       <c r="BL6" t="n">
-        <v>179.2631578947368</v>
+        <v>179.9411764705882</v>
       </c>
       <c r="BM6" t="n">
+        <v>62.41176470588236</v>
+      </c>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>27.36842105263158</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>178.0526315789474</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>69.05263157894737</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BU6" t="n">
         <v>68</v>
       </c>
-      <c r="BN6" t="n">
-        <v>4789.473684210527</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>180.6</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>3150</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>183.3333333333333</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>66.33333333333333</v>
-      </c>
       <c r="BV6" t="n">
-        <v>3000</v>
+        <v>4250</v>
       </c>
       <c r="BW6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX6" t="n">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="BY6" t="n">
-        <v>31</v>
+        <v>24.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="CA6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="CB6" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="CC6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD6" t="n">
-        <v>66</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>4tJ63tfr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45563.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">hernandez l 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20738</v>
+        <v>19400</v>
       </c>
       <c r="F7" t="n">
-        <v>20738</v>
+        <v>19814</v>
       </c>
       <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
+      <c r="V7" t="n">
+        <v>21</v>
+      </c>
+      <c r="W7" t="n">
         <v>5</v>
       </c>
-      <c r="S7" t="n">
-        <v>6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>16</v>
-      </c>
-      <c r="V7" t="n">
-        <v>16</v>
-      </c>
-      <c r="W7" t="n">
-        <v>11</v>
-      </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -2177,74 +2179,74 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>297</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>449</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>250</v>
+        <v>435</v>
       </c>
       <c r="AJ7" t="n">
-        <v>410</v>
+        <v>567</v>
       </c>
       <c r="AK7" t="n">
-        <v>6</v>
+        <v>341</v>
       </c>
       <c r="AL7" t="n">
-        <v>5</v>
+        <v>475</v>
       </c>
       <c r="AM7" t="n">
         <v>2</v>
       </c>
       <c r="AN7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="n">
         <v>0</v>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>KtuTuMN0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="AS7" t="n">
         <v>167</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AT7" t="n">
         <v>1671</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AU7" t="n">
         <v>0</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AV7" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2</v>
       </c>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
@@ -2252,123 +2254,117 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>28.3</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
-        <v>182.3</v>
+        <v>182.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>5200</v>
+        <v>4900</v>
       </c>
       <c r="BG7" t="n">
-        <v>26.3</v>
+        <v>24.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>179.9</v>
+        <v>179.3</v>
       </c>
       <c r="BI7" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>3500</v>
-      </c>
+        <v>66.2</v>
+      </c>
+      <c r="BJ7" t="inlineStr"/>
       <c r="BK7" t="n">
-        <v>27.88235294117647</v>
+        <v>23.69565217391304</v>
       </c>
       <c r="BL7" t="n">
-        <v>177.4705882352941</v>
+        <v>178.7391304347826</v>
       </c>
       <c r="BM7" t="n">
-        <v>67.76470588235294</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4470.588235294118</v>
-      </c>
+        <v>63.1304347826087</v>
+      </c>
+      <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="n">
-        <v>25.91304347826087</v>
+        <v>21.76190476190476</v>
       </c>
       <c r="BP7" t="n">
-        <v>178.9130434782609</v>
+        <v>178.8095238095238</v>
       </c>
       <c r="BQ7" t="n">
-        <v>65.26086956521739</v>
+        <v>57.52380952380953</v>
       </c>
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="n">
-        <v>31.5</v>
+        <v>30.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>189</v>
+        <v>181.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>63</v>
+        <v>66.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>2500</v>
+        <v>3750</v>
       </c>
       <c r="BW7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BX7" t="n">
-        <v>126</v>
+        <v>266</v>
       </c>
       <c r="BY7" t="n">
-        <v>25</v>
+        <v>21.25</v>
       </c>
       <c r="BZ7" t="n">
-        <v>179.3333333333333</v>
+        <v>182.75</v>
       </c>
       <c r="CA7" t="n">
-        <v>64</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>4333.333333333333</v>
-      </c>
+        <v>63.25</v>
+      </c>
+      <c r="CB7" t="inlineStr"/>
       <c r="CC7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD7" t="n">
-        <v>192</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>GGMA209l</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45563.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">gonzalez g  jr 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20500</v>
+        <v>22423</v>
       </c>
       <c r="F8" t="n">
-        <v>19096</v>
+        <v>22423</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -2378,131 +2374,131 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" t="n">
+        <v>15</v>
+      </c>
+      <c r="W8" t="n">
         <v>5</v>
       </c>
-      <c r="R8" t="n">
-        <v>8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V8" t="n">
-        <v>18</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3</v>
-      </c>
       <c r="X8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y8" t="n">
         <v>5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AB8" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AF8" t="n">
         <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>417</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>496</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>365</v>
+        <v>448</v>
       </c>
       <c r="AJ8" t="n">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="AK8" t="n">
-        <v>10</v>
+        <v>361</v>
       </c>
       <c r="AL8" t="n">
+        <v>387</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
         <v>6</v>
       </c>
-      <c r="AM8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN8" t="n">
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="AS8" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AU8" t="n">
         <v>0</v>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AV8" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2</v>
       </c>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
@@ -2510,245 +2506,253 @@
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr">
         <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>26.27272727272727</v>
+        <v>26.09090909090909</v>
       </c>
       <c r="BD8" t="n">
-        <v>179.5454545454545</v>
+        <v>183.5454545454545</v>
       </c>
       <c r="BE8" t="n">
-        <v>69.90909090909091</v>
-      </c>
-      <c r="BF8" t="inlineStr"/>
+        <v>70.18181818181819</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7636.363636363636</v>
+      </c>
       <c r="BG8" t="n">
-        <v>26.2</v>
+        <v>24.18181818181818</v>
       </c>
       <c r="BH8" t="n">
-        <v>182.2</v>
+        <v>179.2727272727273</v>
       </c>
       <c r="BI8" t="n">
-        <v>68.40000000000001</v>
+        <v>63.27272727272727</v>
       </c>
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="n">
-        <v>25.34782608695652</v>
+        <v>24.95</v>
       </c>
       <c r="BL8" t="n">
-        <v>181.7391304347826</v>
+        <v>182.15</v>
       </c>
       <c r="BM8" t="n">
-        <v>63.30434782608695</v>
+        <v>63.9</v>
       </c>
       <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="n">
-        <v>28.65217391304348</v>
+        <v>27.375</v>
       </c>
       <c r="BP8" t="n">
-        <v>181.3478260869565</v>
+        <v>180.7083333333333</v>
       </c>
       <c r="BQ8" t="n">
-        <v>72.34782608695652</v>
+        <v>65.625</v>
       </c>
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="n">
-        <v>23</v>
+        <v>22.75</v>
       </c>
       <c r="BT8" t="n">
-        <v>180</v>
+        <v>177.75</v>
       </c>
       <c r="BU8" t="n">
-        <v>65</v>
+        <v>65.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>2333.333333333333</v>
+        <v>2250</v>
       </c>
       <c r="BW8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX8" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="BY8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BZ8" t="n">
-        <v>183.3333333333333</v>
+        <v>186</v>
       </c>
       <c r="CA8" t="n">
-        <v>66</v>
-      </c>
-      <c r="CB8" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>7000</v>
+      </c>
       <c r="CC8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CD8" t="n">
-        <v>198</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>jRhCHlyE</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45563.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">demianchuk s 
+          <t xml:space="preserve">villarreal a 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30000</v>
+        <v>23112</v>
       </c>
       <c r="F9" t="n">
-        <v>27976</v>
+        <v>19619</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V9" t="n">
         <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE9" t="n">
         <v>13</v>
       </c>
-      <c r="AB9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>14</v>
-      </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>321</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>647</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>241</v>
+        <v>595</v>
       </c>
       <c r="AJ9" t="n">
-        <v>542</v>
+        <v>407</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>528</v>
       </c>
       <c r="AL9" t="n">
+        <v>332</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="AS9" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AU9" t="n">
         <v>0</v>
       </c>
-      <c r="AM9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>63fk89be</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="AV9" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4</v>
       </c>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
@@ -2756,507 +2760,497 @@
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
-        <v>27.33333333333333</v>
+        <v>23.18181818181818</v>
       </c>
       <c r="BD9" t="n">
-        <v>183.6666666666667</v>
+        <v>177.4545454545455</v>
       </c>
       <c r="BE9" t="n">
-        <v>67.11111111111111</v>
+        <v>65.81818181818181</v>
       </c>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="BH9" t="n">
-        <v>180.6</v>
+        <v>179.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>4700</v>
-      </c>
+        <v>69.3</v>
+      </c>
+      <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="n">
-        <v>28.68181818181818</v>
+        <v>22.77777777777778</v>
       </c>
       <c r="BL9" t="n">
-        <v>183.4090909090909</v>
+        <v>177.8888888888889</v>
       </c>
       <c r="BM9" t="n">
-        <v>65.09090909090909</v>
+        <v>67.05555555555556</v>
       </c>
       <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="n">
-        <v>23.85714285714286</v>
+        <v>27.39130434782609</v>
       </c>
       <c r="BP9" t="n">
-        <v>183.5238095238095</v>
+        <v>178.7391304347826</v>
       </c>
       <c r="BQ9" t="n">
-        <v>63.42857142857143</v>
+        <v>67.52173913043478</v>
       </c>
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="BT9" t="n">
-        <v>181.6</v>
+        <v>183</v>
       </c>
       <c r="BU9" t="n">
-        <v>66.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="BV9" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="BW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="CC9" t="n">
         <v>5</v>
       </c>
-      <c r="BX9" t="n">
-        <v>332</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>64.75</v>
-      </c>
-      <c r="CB9" t="inlineStr"/>
-      <c r="CC9" t="n">
-        <v>4</v>
-      </c>
       <c r="CD9" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>SdLZ0mYq</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45563.85416666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">pekmic i 
+          <t xml:space="preserve">vazquez r 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21650</v>
+        <v>20000</v>
       </c>
       <c r="F10" t="n">
-        <v>17328</v>
+        <v>17806</v>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>44</v>
+      </c>
+      <c r="L10" t="n">
+        <v>56</v>
+      </c>
+      <c r="M10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>12</v>
+      </c>
+      <c r="V10" t="n">
+        <v>23</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>404</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>606</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>306</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>517</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="AS10" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AU10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>63</v>
-      </c>
-      <c r="L10" t="n">
-        <v>37</v>
-      </c>
-      <c r="M10" t="n">
-        <v>16</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>22</v>
-      </c>
-      <c r="V10" t="n">
-        <v>10</v>
-      </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>601</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>305</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>525</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>227</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>UFWZoX9L</t>
-        </is>
-      </c>
-      <c r="AQ10" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AV10" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1</v>
       </c>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>26.81818181818182</v>
+        <v>26.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>180.0909090909091</v>
+        <v>185</v>
       </c>
       <c r="BE10" t="n">
-        <v>66.09090909090909</v>
+        <v>67.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>3454.545454545455</v>
+        <v>3700</v>
       </c>
       <c r="BG10" t="n">
         <v>25.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>183.2</v>
+        <v>180.3</v>
       </c>
       <c r="BI10" t="n">
-        <v>66.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="BJ10" t="n">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="BK10" t="n">
-        <v>27.77777777777778</v>
+        <v>25.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>179.7222222222222</v>
+        <v>179.85</v>
       </c>
       <c r="BM10" t="n">
-        <v>66.16666666666667</v>
+        <v>63.1</v>
       </c>
       <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="n">
-        <v>25.27272727272727</v>
+        <v>25.05</v>
       </c>
       <c r="BP10" t="n">
-        <v>178.5</v>
+        <v>182.45</v>
       </c>
       <c r="BQ10" t="n">
-        <v>65.72727272727273</v>
-      </c>
-      <c r="BR10" t="inlineStr"/>
+        <v>66.75</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>3100</v>
+      </c>
       <c r="BS10" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="BT10" t="n">
+        <v>189</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>37</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>186</v>
       </c>
-      <c r="BU10" t="n">
-        <v>72</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>7000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>72</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>182.3333333333333</v>
-      </c>
       <c r="CA10" t="n">
-        <v>63.66666666666666</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>1666.666666666667</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="CB10" t="inlineStr"/>
       <c r="CC10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CD10" t="n">
-        <v>191</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
+          <t>QmZ75TPS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45563.85416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">pekmic i 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23112</v>
+        <v>26000</v>
       </c>
       <c r="F11" t="n">
-        <v>19619</v>
+        <v>24728</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
         <v>6</v>
       </c>
       <c r="U11" t="n">
+        <v>13</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF11" t="n">
         <v>14</v>
       </c>
-      <c r="V11" t="n">
-        <v>12</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="AG11" t="n">
         <v>0</v>
       </c>
-      <c r="X11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AH11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>597</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>337</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>503</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>255</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN11" t="n">
         <v>19</v>
       </c>
-      <c r="AB11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>570</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>682</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>489</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM11" t="n">
+      <c r="AO11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="AS11" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AU11" t="n">
         <v>0</v>
       </c>
-      <c r="AN11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>K4FYmLD9</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="AQ11" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
+      <c r="AV11" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
       </c>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
@@ -3264,241 +3258,245 @@
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="n">
-        <v>22.81818181818182</v>
+        <v>25.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>177.4545454545455</v>
+        <v>179.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>65.81818181818181</v>
-      </c>
-      <c r="BF11" t="inlineStr"/>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5300</v>
+      </c>
       <c r="BG11" t="n">
-        <v>26</v>
+        <v>28.1</v>
       </c>
       <c r="BH11" t="n">
-        <v>182.0909090909091</v>
+        <v>179.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>66.18181818181819</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="BJ11" t="inlineStr"/>
       <c r="BK11" t="n">
-        <v>23.65</v>
+        <v>24.96153846153846</v>
       </c>
       <c r="BL11" t="n">
-        <v>178.8</v>
+        <v>182.3461538461538</v>
       </c>
       <c r="BM11" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4600</v>
-      </c>
+        <v>64.23076923076923</v>
+      </c>
+      <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="n">
-        <v>24.17391304347826</v>
+        <v>27.28571428571428</v>
       </c>
       <c r="BP11" t="n">
-        <v>178</v>
+        <v>182.952380952381</v>
       </c>
       <c r="BQ11" t="n">
-        <v>63.69565217391305</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="BR11" t="inlineStr"/>
-      <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
+      <c r="BS11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>186</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>61.66666666666666</v>
+      </c>
       <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="inlineStr"/>
-      <c r="BX11" t="inlineStr"/>
+      <c r="BW11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>185</v>
+      </c>
       <c r="BY11" t="n">
-        <v>26.8</v>
+        <v>26</v>
       </c>
       <c r="BZ11" t="n">
-        <v>184</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="CA11" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>4800</v>
-      </c>
+        <v>66.33333333333333</v>
+      </c>
+      <c r="CB11" t="inlineStr"/>
       <c r="CC11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CD11" t="n">
-        <v>344</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>MJKw07mj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45563.85416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">touchan r 
+  usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20371</v>
+        <v>21550</v>
       </c>
       <c r="F12" t="n">
-        <v>20868</v>
+        <v>21374</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" t="n">
         <v>11</v>
       </c>
-      <c r="N12" t="n">
+      <c r="W12" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE12" t="n">
         <v>10</v>
       </c>
-      <c r="O12" t="n">
-        <v>6</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="AF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG12" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>19</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>615</v>
-      </c>
       <c r="AH12" t="n">
-        <v>406</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>537</v>
+        <v>704</v>
       </c>
       <c r="AJ12" t="n">
-        <v>337</v>
+        <v>489</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>636</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>399</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="AQ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="AS12" t="n">
         <v>167</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AT12" t="n">
         <v>1671</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AU12" t="n">
         <v>0</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AV12" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2</v>
       </c>
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
@@ -3506,7 +3504,7 @@
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -3515,604 +3513,596 @@
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="BD12" t="n">
-        <v>180.5</v>
+        <v>182.2727272727273</v>
       </c>
       <c r="BE12" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3700</v>
-      </c>
+        <v>73.90909090909091</v>
+      </c>
+      <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="n">
-        <v>25.6</v>
+        <v>27.90909090909091</v>
       </c>
       <c r="BH12" t="n">
-        <v>181.8</v>
+        <v>178.3636363636364</v>
       </c>
       <c r="BI12" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="BJ12" t="inlineStr"/>
+        <v>69.36363636363636</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>8818.181818181818</v>
+      </c>
       <c r="BK12" t="n">
-        <v>24.66666666666667</v>
+        <v>22.52173913043478</v>
       </c>
       <c r="BL12" t="n">
-        <v>179.1428571428571</v>
+        <v>183.8260869565217</v>
       </c>
       <c r="BM12" t="n">
-        <v>68</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4142.857142857143</v>
-      </c>
+        <v>67.69565217391305</v>
+      </c>
+      <c r="BN12" t="inlineStr"/>
       <c r="BO12" t="n">
-        <v>27.60869565217391</v>
+        <v>25.08695652173913</v>
       </c>
       <c r="BP12" t="n">
-        <v>177.4782608695652</v>
+        <v>183.3478260869565</v>
       </c>
       <c r="BQ12" t="n">
-        <v>67.78260869565217</v>
-      </c>
-      <c r="BR12" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>5869.565217391304</v>
+      </c>
       <c r="BS12" t="n">
-        <v>37</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="BT12" t="n">
-        <v>186</v>
+        <v>177.3333333333333</v>
       </c>
       <c r="BU12" t="n">
-        <v>63</v>
-      </c>
-      <c r="BV12" t="inlineStr"/>
+        <v>70.66666666666667</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>5000</v>
+      </c>
       <c r="BW12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BX12" t="n">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="BY12" t="n">
-        <v>23.66666666666667</v>
+        <v>20.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>184</v>
+        <v>182.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>65.66666666666667</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>2666.666666666667</v>
-      </c>
+        <v>55.5</v>
+      </c>
+      <c r="CB12" t="inlineStr"/>
       <c r="CC12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CD12" t="n">
-        <v>197</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>zNOsaR2d</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45563.85416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25000</v>
+        <v>68756</v>
       </c>
       <c r="F13" t="n">
-        <v>19751</v>
+        <v>42312</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L13" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AF13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
-        <v>537</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>427</v>
+        <v>595</v>
       </c>
       <c r="AJ13" t="n">
-        <v>207</v>
+        <v>440</v>
       </c>
       <c r="AK13" t="n">
-        <v>9</v>
+        <v>510</v>
       </c>
       <c r="AL13" t="n">
+        <v>356</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN13" t="n">
         <v>15</v>
       </c>
-      <c r="AM13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="AO13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="AS13" t="n">
         <v>167</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AT13" t="n">
         <v>1671</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AU13" t="n">
         <v>0</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AV13" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1</v>
       </c>
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>180.1111111111111</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>67.44444444444444</v>
-      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="n">
-        <v>26.7</v>
+        <v>28.63636363636364</v>
       </c>
       <c r="BH13" t="n">
-        <v>182.3</v>
+        <v>184.4545454545455</v>
       </c>
       <c r="BI13" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="BJ13" t="inlineStr"/>
+        <v>69.45454545454545</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>4909.090909090909</v>
+      </c>
       <c r="BK13" t="n">
-        <v>21.0625</v>
+        <v>26.82352941176471</v>
       </c>
       <c r="BL13" t="n">
-        <v>178.75</v>
+        <v>181.4117647058823</v>
       </c>
       <c r="BM13" t="n">
-        <v>59.5</v>
+        <v>66.76470588235294</v>
       </c>
       <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="n">
-        <v>24.58823529411765</v>
+        <v>27.05555555555556</v>
       </c>
       <c r="BP13" t="n">
-        <v>178.4705882352941</v>
+        <v>180.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>64.88235294117646</v>
+        <v>65.44444444444444</v>
       </c>
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="n">
-        <v>24.4</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="BT13" t="n">
-        <v>182.6</v>
+        <v>178.6666666666667</v>
       </c>
       <c r="BU13" t="n">
-        <v>66.2</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="BV13" t="n">
-        <v>13800</v>
+        <v>3666.666666666667</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BX13" t="n">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="BY13" t="n">
-        <v>29.33333333333333</v>
+        <v>28</v>
       </c>
       <c r="BZ13" t="n">
-        <v>176.6666666666667</v>
+        <v>185.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>64.66666666666667</v>
-      </c>
-      <c r="CB13" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>3500</v>
+      </c>
       <c r="CC13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CD13" t="n">
-        <v>194</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>xS2QNAuc</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45556.70833333334</v>
+        <v>45563.85416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
+          <t xml:space="preserve">penso t 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>74867</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>25000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>25291</v>
+      </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>54</v>
+      </c>
+      <c r="L14" t="n">
+        <v>46</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>15</v>
+      </c>
+      <c r="V14" t="n">
+        <v>16</v>
+      </c>
+      <c r="W14" t="n">
+        <v>9</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>QJF7WTFB</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>44</v>
-      </c>
-      <c r="L14" t="n">
-        <v>56</v>
-      </c>
-      <c r="M14" t="n">
-        <v>25</v>
-      </c>
-      <c r="N14" t="n">
-        <v>17</v>
-      </c>
-      <c r="O14" t="n">
-        <v>10</v>
-      </c>
-      <c r="P14" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>10</v>
-      </c>
-      <c r="R14" t="n">
-        <v>5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="AI14" t="n">
+        <v>436</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>398</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>359</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>316</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO14" t="n">
         <v>7</v>
       </c>
-      <c r="X14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>349</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>488</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>291</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>434</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="AP14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="AS14" t="n">
         <v>167</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AT14" t="n">
         <v>1671</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AU14" t="n">
         <v>0</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AV14" t="n">
         <v>2024</v>
       </c>
-      <c r="AU14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1</v>
-      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
+      <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="n">
-        <v>27.90909090909091</v>
+        <v>22</v>
       </c>
       <c r="BD14" t="n">
-        <v>178.3636363636364</v>
+        <v>180.1111111111111</v>
       </c>
       <c r="BE14" t="n">
-        <v>69.36363636363636</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8818.181818181818</v>
-      </c>
+        <v>67.44444444444444</v>
+      </c>
+      <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="n">
-        <v>27</v>
+        <v>24.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>69.11111111111111</v>
+        <v>67.3</v>
       </c>
       <c r="BJ14" t="inlineStr"/>
       <c r="BK14" t="n">
-        <v>24</v>
+        <v>22.85</v>
       </c>
       <c r="BL14" t="n">
-        <v>184.6521739130435</v>
+        <v>178.65</v>
       </c>
       <c r="BM14" t="n">
-        <v>65.1304347826087</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>3652.173913043478</v>
-      </c>
+        <v>62.8</v>
+      </c>
+      <c r="BN14" t="inlineStr"/>
       <c r="BO14" t="n">
-        <v>25.66666666666667</v>
+        <v>22.61111111111111</v>
       </c>
       <c r="BP14" t="n">
-        <v>178.7142857142857</v>
+        <v>182.0555555555555</v>
       </c>
       <c r="BQ14" t="n">
-        <v>67</v>
+        <v>64.5</v>
       </c>
       <c r="BR14" t="inlineStr"/>
       <c r="BS14" t="n">
-        <v>20.5</v>
+        <v>22.75</v>
       </c>
       <c r="BT14" t="n">
-        <v>182.5</v>
+        <v>184</v>
       </c>
       <c r="BU14" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>2750</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>251</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="CA14" t="n">
         <v>55.5</v>
       </c>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX14" t="n">
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD14" t="n">
         <v>111</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>4500</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>GI1UMUf3</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45556.625</v>
+        <v>45563.85416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">bazakos f 
   usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">yankee stadium
-  new york  ny </t>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>54251</v>
+        <v>18500</v>
       </c>
       <c r="F15" t="n">
-        <v>44738</v>
+        <v>18837</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -4122,400 +4112,434 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L15" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M15" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
+        <v>9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
         <v>7</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
       <c r="T15" t="n">
         <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="V15" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="W15" t="n">
         <v>8</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="n">
         <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF15" t="n">
         <v>10</v>
       </c>
-      <c r="AB15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>20</v>
-      </c>
       <c r="AG15" t="n">
-        <v>454</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>520</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>368</v>
+        <v>487</v>
       </c>
       <c r="AJ15" t="n">
-        <v>424</v>
+        <v>470</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>405</v>
       </c>
       <c r="AL15" t="n">
-        <v>13</v>
+        <v>385</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>6gpXy3vi</t>
-        </is>
-      </c>
-      <c r="AQ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="AS15" t="n">
         <v>167</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AT15" t="n">
         <v>1671</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AU15" t="n">
         <v>0</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AV15" t="n">
         <v>2024</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5</v>
       </c>
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="n">
-        <v>25.44444444444444</v>
+        <v>25.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>179.1111111111111</v>
+        <v>184.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>67.33333333333333</v>
+        <v>71.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>4777.777777777777</v>
+        <v>5900</v>
       </c>
       <c r="BG15" t="n">
-        <v>25.09090909090909</v>
+        <v>26.8</v>
       </c>
       <c r="BH15" t="n">
-        <v>181.4545454545455</v>
+        <v>181.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>71.27272727272727</v>
-      </c>
-      <c r="BJ15" t="inlineStr"/>
+        <v>67.5</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>8100</v>
+      </c>
       <c r="BK15" t="n">
-        <v>20.52173913043478</v>
+        <v>25.75</v>
       </c>
       <c r="BL15" t="n">
-        <v>182.0434782608696</v>
+        <v>183.8125</v>
       </c>
       <c r="BM15" t="n">
-        <v>62.30434782608695</v>
-      </c>
-      <c r="BN15" t="inlineStr"/>
+        <v>66.5625</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4125</v>
+      </c>
       <c r="BO15" t="n">
-        <v>24.17647058823529</v>
+        <v>25.94117647058824</v>
       </c>
       <c r="BP15" t="n">
-        <v>183.2941176470588</v>
+        <v>175.3529411764706</v>
       </c>
       <c r="BQ15" t="n">
-        <v>68.17647058823529</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>4000</v>
-      </c>
+        <v>66.05882352941177</v>
+      </c>
+      <c r="BR15" t="inlineStr"/>
       <c r="BS15" t="n">
         <v>22</v>
       </c>
       <c r="BT15" t="n">
-        <v>183</v>
+        <v>181.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>60.5</v>
+        <v>55</v>
       </c>
       <c r="BV15" t="inlineStr"/>
       <c r="BW15" t="n">
         <v>2</v>
       </c>
       <c r="BX15" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BY15" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="BZ15" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="CA15" t="n">
-        <v>72.75</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>6750</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="CB15" t="inlineStr"/>
       <c r="CC15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CD15" t="n">
-        <v>291</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>p2PIpxK5</t>
+          <t>ID0yCpq9</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45557.75</v>
+        <v>45560.97916666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">meyer b 
+          <t xml:space="preserve">villarreal a 
   usa </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">protective stadium
-  birmingham  al </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>47100</v>
+        <v>22000</v>
       </c>
       <c r="F16" t="n">
-        <v>4279</v>
+        <v>1402</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>rysqEtSu</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>UJTiXUTf</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="n">
         <v>6</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>621</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>480</v>
+        <v>3</v>
       </c>
       <c r="AI16" t="n">
-        <v>547</v>
+        <v>630</v>
       </c>
       <c r="AJ16" t="n">
-        <v>415</v>
+        <v>594</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>16</v>
+        <v>462</v>
       </c>
       <c r="AM16" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AN16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>v7f8zS64</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>zVUAOJSG</t>
-        </is>
-      </c>
-      <c r="AQ16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="AS16" t="n">
         <v>167</v>
       </c>
-      <c r="AR16" t="n">
-        <v>1673</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
       <c r="AT16" t="n">
+        <v>1672</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
         <v>2024</v>
       </c>
-      <c r="AU16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>6</v>
-      </c>
+      <c r="AW16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>28.81818181818182</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>181.5454545454545</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>73.63636363636364</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>19000</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>27.36363636363636</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>66</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>3454.545454545455</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>29.4375</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>183</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>70.375</v>
+      </c>
       <c r="BN16" t="inlineStr"/>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr"/>
-      <c r="BR16" t="inlineStr"/>
+      <c r="BO16" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>176.4090909090909</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>65.81818181818181</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>3363.636363636364</v>
+      </c>
       <c r="BS16" t="inlineStr"/>
       <c r="BT16" t="inlineStr"/>
       <c r="BU16" t="inlineStr"/>
@@ -4532,84 +4556,86 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vPOMqdZB</t>
+          <t>Eed8egYN</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45557.70833333334</v>
+        <v>45564.89583333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">koroleva e 
+          <t xml:space="preserve">stevis b 
   usa </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">rio grande credit union field at isotopes park
-  albuquerque  nm </t>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13500</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>11569</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11569</v>
+      </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>dI5p0xzH</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>faQG6GQT</t>
-        </is>
-      </c>
       <c r="K17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
         <v>11</v>
       </c>
-      <c r="N17" t="n">
-        <v>10</v>
-      </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="n">
         <v>3</v>
@@ -4617,77 +4643,77 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="n">
         <v>13</v>
       </c>
       <c r="AG17" t="n">
-        <v>496</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>570</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>440</v>
+        <v>388</v>
       </c>
       <c r="AJ17" t="n">
-        <v>478</v>
+        <v>530</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>307</v>
       </c>
       <c r="AL17" t="n">
-        <v>14</v>
+        <v>446</v>
       </c>
       <c r="AM17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO17" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
         <is>
           <t>Cf83muss</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>tvIcCmLN</t>
-        </is>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="AS17" t="n">
         <v>167</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AT17" t="n">
         <v>1673</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AU17" t="n">
         <v>0</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AV17" t="n">
         <v>2024</v>
       </c>
-      <c r="AU17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ17" t="n">
+      <c r="AW17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX17" t="n">
         <v>12</v>
       </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
@@ -4698,9 +4724,15 @@
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr"/>
       <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="inlineStr"/>
-      <c r="BM17" t="inlineStr"/>
+      <c r="BK17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>184</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>59.5</v>
+      </c>
       <c r="BN17" t="inlineStr"/>
       <c r="BO17" t="inlineStr"/>
       <c r="BP17" t="inlineStr"/>
@@ -4722,166 +4754,132 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>6exiWx5C</t>
+          <t>z5c4dZIH</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45557.66666666666</v>
+        <v>45564.79166666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">fierro r 
+          <t xml:space="preserve">snyder t 
   usa </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyworth stadium
-  hamtramck  mi </t>
+          <t xml:space="preserve">laney college football stadium
+  oakland  ca </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7933</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>5500</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4190</v>
+      </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>dAoaDOc7</t>
+          <t>zLYVwGMm</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>nRGIlQ2T</t>
+          <t>OEz4Fa6C</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L18" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>20</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>437</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>426</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>316</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>313</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>lKNscApp</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>IorPEfz8</t>
-        </is>
-      </c>
-      <c r="AQ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="AS18" t="n">
         <v>167</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AT18" t="n">
         <v>1673</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AU18" t="n">
         <v>0</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AV18" t="n">
         <v>2024</v>
       </c>
-      <c r="AU18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>11</v>
-      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
@@ -4916,83 +4914,81 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>GQJsg0CP</t>
+          <t>46dq1c4n</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45563.97916666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">corrigan m 
+          <t xml:space="preserve">radosav c 
   usa </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">cashman field
-  las vegas  nv </t>
+          <t xml:space="preserve">wild horse pass stadium
+  chandler  az </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12500</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2240</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>vVWDE67k</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>z3BFwb83</t>
-        </is>
-      </c>
       <c r="K19" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="L19" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
         <v>5</v>
       </c>
-      <c r="P19" t="n">
-        <v>3</v>
-      </c>
       <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
         <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="n">
         <v>1</v>
@@ -5003,81 +4999,77 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>643</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="n">
-        <v>349</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>580</v>
+        <v>396</v>
       </c>
       <c r="AJ19" t="n">
-        <v>261</v>
+        <v>562</v>
       </c>
       <c r="AK19" t="n">
+        <v>329</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>514</v>
+      </c>
+      <c r="AM19" t="n">
         <v>16</v>
       </c>
-      <c r="AL19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>3</v>
-      </c>
       <c r="AN19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO19" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>xYs9X2t2</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
         <is>
           <t>zDeq7OqE</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>URfp4iBR</t>
-        </is>
-      </c>
-      <c r="AQ19" t="n">
+      <c r="AS19" t="n">
         <v>167</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AT19" t="n">
         <v>1673</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AU19" t="n">
         <v>0</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AV19" t="n">
         <v>2024</v>
       </c>
-      <c r="AU19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3</v>
-      </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>13</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -5092,9 +5084,15 @@
       <c r="BL19" t="inlineStr"/>
       <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr"/>
-      <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
-      <c r="BQ19" t="inlineStr"/>
+      <c r="BO19" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>59.2</v>
+      </c>
       <c r="BR19" t="inlineStr"/>
       <c r="BS19" t="inlineStr"/>
       <c r="BT19" t="inlineStr"/>
@@ -5112,164 +5110,164 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Qa9Hnbkg</t>
+          <t>QFcu2wkt</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45563.95833333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">flores g 
+          <t xml:space="preserve">ndiaye a 
   usa </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">wild horse pass stadium
-  chandler  az </t>
+          <t xml:space="preserve">cardinale stadium
+  seaside  ca </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F20" t="n">
-        <v>4844</v>
+        <v>4742</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CWnNB64j</t>
+          <t>0vY9Fnhq</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8njPmvTl</t>
+          <t>dAoaDOc7</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="L20" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20" t="n">
         <v>3</v>
       </c>
       <c r="Y20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4</v>
       </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>552</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>377</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="AJ20" t="n">
-        <v>294</v>
+        <v>436</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>492</v>
       </c>
       <c r="AL20" t="n">
+        <v>350</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>4jMOGgL1</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="AS20" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1673</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AW20" t="n">
         <v>12</v>
       </c>
-      <c r="AM20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>xYs9X2t2</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>6X9nrWKc</t>
-        </is>
-      </c>
-      <c r="AQ20" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1673</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>10</v>
-      </c>
+      <c r="AX20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
@@ -5284,18 +5282,10 @@
       <c r="BL20" t="inlineStr"/>
       <c r="BM20" t="inlineStr"/>
       <c r="BN20" t="inlineStr"/>
-      <c r="BO20" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>186.125</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>58.875</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1125</v>
-      </c>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
       <c r="BS20" t="inlineStr"/>
       <c r="BT20" t="inlineStr"/>
       <c r="BU20" t="inlineStr"/>
@@ -5312,44 +5302,44 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hnB9lKKt</t>
+          <t>pG4iayZb</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45556.95833333334</v>
+        <v>45563.89583333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia e 
+          <t xml:space="preserve">demianchuk s 
   usa </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardinale stadium
-  seaside  ca </t>
+          <t xml:space="preserve">toyota field
+  san antonio  tx </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6000</v>
+        <v>8296</v>
       </c>
       <c r="F21" t="n">
-        <v>3912</v>
+        <v>6620</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0vY9Fnhq</t>
+          <t>8njPmvTl</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>llkqyHYq</t>
+          <t>EabuZlYo</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -5359,116 +5349,120 @@
         <v>46</v>
       </c>
       <c r="M21" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" t="n">
         <v>18</v>
       </c>
-      <c r="N21" t="n">
-        <v>11</v>
-      </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>339</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>319</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>244</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>216</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO21" t="n">
         <v>10</v>
       </c>
-      <c r="AG21" t="n">
-        <v>639</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>523</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>572</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>454</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>4jMOGgL1</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>McXMYtMJ</t>
-        </is>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="AP21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="AS21" t="n">
         <v>167</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AT21" t="n">
         <v>1673</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2024</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13</v>
+      </c>
       <c r="AY21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="inlineStr"/>
@@ -5504,29 +5498,29 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>zVteVdKI</t>
+          <t>ziIVsz4O</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45556.91666666666</v>
+        <v>45563.875</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">bensalah n 
+          <t xml:space="preserve">berna rico s 
   usa </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">southwest university park
-  el paso  tx </t>
+          <t xml:space="preserve">weidner field
+  colorado springs  co </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F22" t="n">
-        <v>5422</v>
+        <v>8023</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -5536,57 +5530,57 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MRumD0sn</t>
+          <t>rmLxuq9b</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>rmLxuq9b</t>
+          <t>faQG6GQT</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
@@ -5594,74 +5588,74 @@
         <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AF22" t="n">
         <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>402</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>357</v>
+        <v>5</v>
       </c>
       <c r="AI22" t="n">
-        <v>308</v>
+        <v>476</v>
       </c>
       <c r="AJ22" t="n">
-        <v>252</v>
+        <v>487</v>
       </c>
       <c r="AK22" t="n">
-        <v>12</v>
+        <v>380</v>
       </c>
       <c r="AL22" t="n">
-        <v>12</v>
+        <v>411</v>
       </c>
       <c r="AM22" t="n">
         <v>5</v>
       </c>
       <c r="AN22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP22" t="n">
         <v>7</v>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>U31kqHhr</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>6V8Ndys8</t>
         </is>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="AS22" t="n">
         <v>167</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AT22" t="n">
         <v>1673</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AU22" t="n">
         <v>0</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AV22" t="n">
         <v>2024</v>
       </c>
-      <c r="AU22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>5</v>
       </c>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>9</v>
-      </c>
+      <c r="AX22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>
@@ -5696,164 +5690,164 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>S4wmXIk6</t>
+          <t>ptlrYbz0</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45563.85416666666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ndiaye a 
+          <t xml:space="preserve">bensalah n 
   usa </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">patriots point soccer complex
-  mount pleasant  sc </t>
+          <t xml:space="preserve">lynn family stadium
+  louisville  ky </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5000</v>
+        <v>15304</v>
       </c>
       <c r="F23" t="n">
-        <v>4366</v>
+        <v>6197</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2wA8p3yn</t>
+          <t>nRGIlQ2T</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>AohGC74A</t>
+          <t>MoS88xdH</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L23" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
         <v>9</v>
       </c>
-      <c r="P23" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4</v>
-      </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AF23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AG23" t="n">
-        <v>550</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>388</v>
+        <v>4</v>
       </c>
       <c r="AI23" t="n">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="AJ23" t="n">
-        <v>327</v>
+        <v>499</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>414</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="AM23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="AS23" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1673</v>
+      </c>
+      <c r="AU23" t="n">
         <v>0</v>
       </c>
-      <c r="AN23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>zPVO4eiP</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>SUJLjQfn</t>
-        </is>
-      </c>
-      <c r="AQ23" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1673</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
+      <c r="AV23" t="n">
         <v>2024</v>
       </c>
-      <c r="AU23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="n">
+      <c r="AW23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX23" t="n">
         <v>10</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>5</v>
-      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
@@ -5888,83 +5882,83 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>n9ADmvzm</t>
+          <t>EsHZtfJU</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45563.83333333334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">scheer j 
+          <t xml:space="preserve">thompson m 
   usa </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">wakemed soccer park
-  cary  nc </t>
+          <t xml:space="preserve">michael a  carroll stadium
+  indianapolis  in </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10000</v>
+        <v>12111</v>
       </c>
       <c r="F24" t="n">
-        <v>2478</v>
+        <v>10145</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>OnB4oqMu</t>
+          <t>dtMNCXyk</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>dtMNCXyk</t>
+          <t>UJTiXUTf</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="L24" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="M24" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="N24" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
         <v>8</v>
       </c>
       <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="n">
         <v>9</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>1</v>
@@ -5975,72 +5969,80 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>420</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>353</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>349</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>272</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="AS24" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1673</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX24" t="n">
         <v>8</v>
       </c>
-      <c r="AF24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>327</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>506</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>237</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>429</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>31</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>0YXKhAXq</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>txm4BKVR</t>
-        </is>
-      </c>
-      <c r="AQ24" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1673</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
@@ -6076,160 +6078,164 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>6BQEoI4a</t>
+          <t>nVol0HJh</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45563.83333333334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">kilpatrick a 
+          <t xml:space="preserve">osmanovic e 
   usa </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">beirne stadium
-  pawtucket  ri </t>
+          <t xml:space="preserve">highmark stadium
+  pittsburgh  pa </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5252</v>
+        <v>5000</v>
       </c>
       <c r="F25" t="n">
-        <v>5252</v>
+        <v>5537</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EabuZlYo</t>
+          <t>trYG3CIh</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>OEz4Fa6C</t>
+          <t>rysqEtSu</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="L25" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="M25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" t="n">
         <v>7</v>
       </c>
-      <c r="P25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>450</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="n">
-        <v>363</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="n">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="AJ25" t="n">
-        <v>259</v>
+        <v>536</v>
       </c>
       <c r="AK25" t="n">
-        <v>24</v>
+        <v>281</v>
       </c>
       <c r="AL25" t="n">
-        <v>29</v>
+        <v>420</v>
       </c>
       <c r="AM25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="AS25" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1673</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX25" t="n">
         <v>12</v>
       </c>
-      <c r="AN25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>n9nYS6gm</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>vucevHGn</t>
-        </is>
-      </c>
-      <c r="AQ25" t="n">
-        <v>167</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1673</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>20</v>
-      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr"/>
@@ -6264,86 +6270,86 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>ELuaUGZO</t>
+          <t>IT2acF3B</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45556.83333333334</v>
+        <v>45563.66666666666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">nichols a 
+          <t xml:space="preserve">hassan m 
   usa </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">trinity health stadium
-  east hartford  ct </t>
+          <t xml:space="preserve">southwest university park
+  el paso  tx </t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>10000</v>
       </c>
       <c r="F26" t="n">
-        <v>5500</v>
+        <v>4014</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Ew2P6PKC</t>
+          <t>MRumD0sn</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>zLYVwGMm</t>
+          <t>OnB4oqMu</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="L26" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="M26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
         <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
         <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
@@ -6351,81 +6357,77 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD26" t="n">
         <v>6</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>533</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>350</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>452</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>292</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP26" t="n">
         <v>5</v>
       </c>
-      <c r="AE26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>414</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>467</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>336</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>374</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>39</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>xYHj0Fat</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>A7iCSGMH</t>
-        </is>
-      </c>
-      <c r="AQ26" t="n">
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>U31kqHhr</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="AS26" t="n">
         <v>167</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>1673</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AU26" t="n">
         <v>0</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AV26" t="n">
         <v>2024</v>
       </c>
-      <c r="AU26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3</v>
-      </c>
       <c r="AW26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="inlineStr"/>
@@ -6457,6 +6459,198 @@
       <c r="CC26" t="inlineStr"/>
       <c r="CD26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>hSSQrGlI</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45560.97916666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">griggs j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">championship soccer stadium
+  irvine  ca </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3018</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>32</v>
+      </c>
+      <c r="L27" t="n">
+        <v>68</v>
+      </c>
+      <c r="M27" t="n">
+        <v>13</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>5</v>
+      </c>
+      <c r="X27" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>301</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>614</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>235</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>558</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>McXMYtMJ</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>xYs9X2t2</t>
+        </is>
+      </c>
+      <c r="AS27" t="n">
+        <v>167</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1673</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+      <c r="BO27" t="inlineStr"/>
+      <c r="BP27" t="inlineStr"/>
+      <c r="BQ27" t="inlineStr"/>
+      <c r="BR27" t="inlineStr"/>
+      <c r="BS27" t="inlineStr"/>
+      <c r="BT27" t="inlineStr"/>
+      <c r="BU27" t="inlineStr"/>
+      <c r="BV27" t="inlineStr"/>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="inlineStr"/>
+      <c r="BZ27" t="inlineStr"/>
+      <c r="CA27" t="inlineStr"/>
+      <c r="CB27" t="inlineStr"/>
+      <c r="CC27" t="inlineStr"/>
+      <c r="CD27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
